--- a/Nilai PTS dan ASAS Ganjil 2025-2026/Olah Nilai ASAS/XI ASAS/XI-2 PAS INFORMATIKA SMT GANJIL TH.2025_2026  (Jawaban).xlsx
+++ b/Nilai PTS dan ASAS Ganjil 2025-2026/Olah Nilai ASAS/XI ASAS/XI-2 PAS INFORMATIKA SMT GANJIL TH.2025_2026  (Jawaban).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21750" windowHeight="11950"/>
+    <workbookView windowWidth="28800" windowHeight="12420"/>
   </bookViews>
   <sheets>
     <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
@@ -1133,7 +1133,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1147,7 +1147,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1161,7 +1161,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1176,7 +1176,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1190,7 +1190,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1204,7 +1204,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1218,7 +1218,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1232,7 +1232,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1246,7 +1246,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1260,7 +1260,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1274,7 +1274,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1288,7 +1288,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1302,7 +1302,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1316,7 +1316,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1330,7 +1330,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1344,7 +1344,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1358,7 +1358,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1372,7 +1372,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1386,7 +1386,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1400,7 +1400,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1414,7 +1414,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1428,7 +1428,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1442,7 +1442,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1456,7 +1456,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1470,7 +1470,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1484,7 +1484,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1498,7 +1498,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1512,7 +1512,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1526,7 +1526,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1540,7 +1540,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1554,7 +1554,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1568,7 +1568,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1582,7 +1582,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1596,7 +1596,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1610,7 +1610,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1624,7 +1624,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1638,7 +1638,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1652,7 +1652,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1666,7 +1666,7 @@
     <dxf>
       <font>
         <name val="Arial"/>
-        <scheme val="minor"/>
+        <scheme val="none"/>
         <charset val="134"/>
         <family val="0"/>
         <b val="0"/>
@@ -1719,7 +1719,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{E4DE38BE-277D-75CC-AEBC-2F6947436F0A}">
+    <tableStyle name="Form Responses 1-style" pivot="0" count="4" xr9:uid="{00154D8E-CB9D-BDEF-8FFF-40690CF690BE}">
       <tableStyleElement type="wholeTable" dxfId="42"/>
       <tableStyleElement type="headerRow" dxfId="41"/>
       <tableStyleElement type="firstRowStripe" dxfId="40"/>
@@ -2078,6 +2078,11 @@
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext uri="{0b15fc19-7d7d-44ad-8c2d-2c3a37ce22c3}">
+        <chartProps xmlns="https://web.wps.cn/et/2018/main" chartId="{260d85c5-6968-4c6a-a4c8-1bbb67d64378}"/>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2693,7 +2698,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:AM35">
-  <sortState ref="A2:AM35">
+  <sortState ref="A1:AM35">
     <sortCondition ref="E2:E35"/>
   </sortState>
   <tableColumns count="39">
@@ -2941,7 +2946,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AM35"/>
+  <dimension ref="A1:AM42"/>
   <sheetFormatPr defaultColWidth="12.6285714285714" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="18.8761904761905" customWidth="1"/>
@@ -7143,6 +7148,24 @@
         <v>74</v>
       </c>
     </row>
+    <row r="40" customHeight="1" spans="1:39">
+      <c r="A40">
+        <f>AVERAGE(C2:C35)</f>
+        <v>89.8529411764706</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:39">
+      <c r="A41">
+        <f>MAX(C2:C35)</f>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="1:39">
+      <c r="A42">
+        <f>MIN(C2:C35)</f>
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
